--- a/docs/hipoteques.xlsx
+++ b/docs/hipoteques.xlsx
@@ -1653,42 +1653,6 @@
           <t>202602</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>59531</v>
-      </c>
-      <c r="F2" t="n">
-        <v>58459</v>
-      </c>
-      <c r="J2" t="n">
-        <v>46661</v>
-      </c>
-      <c r="N2" t="n">
-        <v>458</v>
-      </c>
-      <c r="R2" t="n">
-        <v>11340</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1072</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11478708</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11150811</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8125195</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>408039</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2617577</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>327897</v>
-      </c>
       <c r="AX2" t="n">
         <v>69425</v>
       </c>
@@ -1714,42 +1678,6 @@
           <t>202601</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>59349</v>
-      </c>
-      <c r="F3" t="n">
-        <v>58406</v>
-      </c>
-      <c r="J3" t="n">
-        <v>45563</v>
-      </c>
-      <c r="N3" t="n">
-        <v>507</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12336</v>
-      </c>
-      <c r="V3" t="n">
-        <v>943</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11181160</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>10983495</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>7895166</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>477874</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2610455</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>197665</v>
-      </c>
       <c r="AX3" t="n">
         <v>55864</v>
       </c>
@@ -1775,42 +1703,6 @@
           <t>202512</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>49384</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48585</v>
-      </c>
-      <c r="J4" t="n">
-        <v>39330</v>
-      </c>
-      <c r="N4" t="n">
-        <v>404</v>
-      </c>
-      <c r="R4" t="n">
-        <v>8851</v>
-      </c>
-      <c r="V4" t="n">
-        <v>799</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>9949811</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>9782222</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>6665198</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>424379</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2692645</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>167589</v>
-      </c>
       <c r="AX4" t="n">
         <v>59062</v>
       </c>
@@ -1836,42 +1728,6 @@
           <t>202511</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>49271</v>
-      </c>
-      <c r="F5" t="n">
-        <v>48290</v>
-      </c>
-      <c r="J5" t="n">
-        <v>37841</v>
-      </c>
-      <c r="N5" t="n">
-        <v>487</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9962</v>
-      </c>
-      <c r="V5" t="n">
-        <v>981</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9878599</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>9608183</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>6528887</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>545099</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2534197</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>270416</v>
-      </c>
       <c r="AX5" t="n">
         <v>54979</v>
       </c>
@@ -1897,42 +1753,6 @@
           <t>202510</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>55762</v>
-      </c>
-      <c r="F6" t="n">
-        <v>54928</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43319</v>
-      </c>
-      <c r="N6" t="n">
-        <v>368</v>
-      </c>
-      <c r="R6" t="n">
-        <v>11241</v>
-      </c>
-      <c r="V6" t="n">
-        <v>834</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>10695781</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10510935</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>7397618</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>265620</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2847697</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>184846</v>
-      </c>
       <c r="AX6" t="n">
         <v>62184</v>
       </c>
@@ -1958,42 +1778,6 @@
           <t>202509</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>66960</v>
-      </c>
-      <c r="F7" t="n">
-        <v>65863</v>
-      </c>
-      <c r="J7" t="n">
-        <v>52198</v>
-      </c>
-      <c r="N7" t="n">
-        <v>367</v>
-      </c>
-      <c r="R7" t="n">
-        <v>13298</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1097</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>12252940</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11988179</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>8721246</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>443243</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2823690</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>264761</v>
-      </c>
       <c r="AX7" t="n">
         <v>67202</v>
       </c>
@@ -2019,42 +1803,6 @@
           <t>202508</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>59261</v>
-      </c>
-      <c r="F8" t="n">
-        <v>58227</v>
-      </c>
-      <c r="J8" t="n">
-        <v>46120</v>
-      </c>
-      <c r="N8" t="n">
-        <v>479</v>
-      </c>
-      <c r="R8" t="n">
-        <v>11628</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1034</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>11566816</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11360334</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>7914755</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>528921</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2916658</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>206482</v>
-      </c>
       <c r="AX8" t="n">
         <v>52829</v>
       </c>
@@ -2080,42 +1828,6 @@
           <t>202507</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>43089</v>
-      </c>
-      <c r="F9" t="n">
-        <v>42407</v>
-      </c>
-      <c r="J9" t="n">
-        <v>33271</v>
-      </c>
-      <c r="N9" t="n">
-        <v>272</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8864</v>
-      </c>
-      <c r="V9" t="n">
-        <v>682</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8129264</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>7990659</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>5644431</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>370208</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1976020</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>138605</v>
-      </c>
       <c r="AX9" t="n">
         <v>40817</v>
       </c>
@@ -2141,42 +1853,6 @@
           <t>202506</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>57299</v>
-      </c>
-      <c r="F10" t="n">
-        <v>56431</v>
-      </c>
-      <c r="J10" t="n">
-        <v>45067</v>
-      </c>
-      <c r="N10" t="n">
-        <v>419</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10945</v>
-      </c>
-      <c r="V10" t="n">
-        <v>868</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>10385897</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>10194623</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>7359757</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>352831</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2482035</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>191274</v>
-      </c>
       <c r="AX10" t="n">
         <v>58877</v>
       </c>
@@ -2202,42 +1878,6 @@
           <t>202505</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>53438</v>
-      </c>
-      <c r="F11" t="n">
-        <v>52654</v>
-      </c>
-      <c r="J11" t="n">
-        <v>41834</v>
-      </c>
-      <c r="N11" t="n">
-        <v>497</v>
-      </c>
-      <c r="R11" t="n">
-        <v>10323</v>
-      </c>
-      <c r="V11" t="n">
-        <v>784</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>9778252</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>9604368</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>7043297</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>469554</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2091517</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>173884</v>
-      </c>
       <c r="AX11" t="n">
         <v>59150</v>
       </c>
@@ -2263,42 +1903,6 @@
           <t>202504</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>54744</v>
-      </c>
-      <c r="F12" t="n">
-        <v>53860</v>
-      </c>
-      <c r="J12" t="n">
-        <v>42274</v>
-      </c>
-      <c r="N12" t="n">
-        <v>382</v>
-      </c>
-      <c r="R12" t="n">
-        <v>11204</v>
-      </c>
-      <c r="V12" t="n">
-        <v>884</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>9367997</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>9168572</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>6685742</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>309641</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2173189</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>199425</v>
-      </c>
       <c r="AX12" t="n">
         <v>58125</v>
       </c>
@@ -2323,42 +1927,6 @@
         <is>
           <t>202503</t>
         </is>
-      </c>
-      <c r="B13" t="n">
-        <v>50562</v>
-      </c>
-      <c r="F13" t="n">
-        <v>49869</v>
-      </c>
-      <c r="J13" t="n">
-        <v>39176</v>
-      </c>
-      <c r="N13" t="n">
-        <v>349</v>
-      </c>
-      <c r="R13" t="n">
-        <v>10344</v>
-      </c>
-      <c r="V13" t="n">
-        <v>693</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>8620259</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>8295254</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>6106866</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>337654</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1850734</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>325005</v>
       </c>
       <c r="AX13" t="n">
         <v>55304</v>

--- a/docs/hipoteques.xlsx
+++ b/docs/hipoteques.xlsx
@@ -1653,23 +1653,41 @@
           <t>202602</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>69425</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>67679</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>50582</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>762</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>16335</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1746</v>
+      <c r="B2" t="n">
+        <v>59531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>58459</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46661</v>
+      </c>
+      <c r="N2" t="n">
+        <v>458</v>
+      </c>
+      <c r="R2" t="n">
+        <v>11340</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1072</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11478708</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11150811</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8125195</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>408039</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2617577</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>327897</v>
       </c>
     </row>
     <row r="3">
@@ -1678,23 +1696,41 @@
           <t>202601</t>
         </is>
       </c>
-      <c r="AX3" t="n">
-        <v>55864</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>54325</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>41522</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>602</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>12201</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1539</v>
+      <c r="B3" t="n">
+        <v>59349</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58406</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45563</v>
+      </c>
+      <c r="N3" t="n">
+        <v>507</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12336</v>
+      </c>
+      <c r="V3" t="n">
+        <v>943</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>11181160</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10983495</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>7895166</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>477874</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2610455</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>197665</v>
       </c>
     </row>
     <row r="4">
@@ -1703,23 +1739,41 @@
           <t>202512</t>
         </is>
       </c>
-      <c r="AX4" t="n">
-        <v>59062</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>57801</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>42888</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>779</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>14134</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1261</v>
+      <c r="B4" t="n">
+        <v>49384</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48585</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39330</v>
+      </c>
+      <c r="N4" t="n">
+        <v>404</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8851</v>
+      </c>
+      <c r="V4" t="n">
+        <v>799</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9949811</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9782222</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6665198</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>424379</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2692645</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>167589</v>
       </c>
     </row>
     <row r="5">
@@ -1728,23 +1782,41 @@
           <t>202511</t>
         </is>
       </c>
-      <c r="AX5" t="n">
-        <v>54979</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>53564</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>40101</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>704</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>12759</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1415</v>
+      <c r="B5" t="n">
+        <v>49271</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48290</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37841</v>
+      </c>
+      <c r="N5" t="n">
+        <v>487</v>
+      </c>
+      <c r="R5" t="n">
+        <v>9962</v>
+      </c>
+      <c r="V5" t="n">
+        <v>981</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9878599</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9608183</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>6528887</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>545099</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2534197</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>270416</v>
       </c>
     </row>
     <row r="6">
@@ -1753,23 +1825,41 @@
           <t>202510</t>
         </is>
       </c>
-      <c r="AX6" t="n">
-        <v>62184</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>60663</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>45493</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1173</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>13997</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1521</v>
+      <c r="B6" t="n">
+        <v>55762</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54928</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43319</v>
+      </c>
+      <c r="N6" t="n">
+        <v>368</v>
+      </c>
+      <c r="R6" t="n">
+        <v>11241</v>
+      </c>
+      <c r="V6" t="n">
+        <v>834</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10695781</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10510935</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7397618</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>265620</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2847697</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>184846</v>
       </c>
     </row>
     <row r="7">
@@ -1778,23 +1868,41 @@
           <t>202509</t>
         </is>
       </c>
-      <c r="AX7" t="n">
-        <v>67202</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>65643</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>48350</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>829</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>16464</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1559</v>
+      <c r="B7" t="n">
+        <v>66960</v>
+      </c>
+      <c r="F7" t="n">
+        <v>65863</v>
+      </c>
+      <c r="J7" t="n">
+        <v>52198</v>
+      </c>
+      <c r="N7" t="n">
+        <v>367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>13298</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1097</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12252940</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11988179</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8721246</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>443243</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2823690</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>264761</v>
       </c>
     </row>
     <row r="8">
@@ -1803,23 +1911,41 @@
           <t>202508</t>
         </is>
       </c>
-      <c r="AX8" t="n">
-        <v>52829</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>51315</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>38168</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>875</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>12272</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1514</v>
+      <c r="B8" t="n">
+        <v>59261</v>
+      </c>
+      <c r="F8" t="n">
+        <v>58227</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46120</v>
+      </c>
+      <c r="N8" t="n">
+        <v>479</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11628</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1034</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>11566816</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>11360334</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>7914755</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>528921</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2916658</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>206482</v>
       </c>
     </row>
     <row r="9">
@@ -1828,23 +1954,41 @@
           <t>202507</t>
         </is>
       </c>
-      <c r="AX9" t="n">
-        <v>40817</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>39753</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>29742</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>443</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>9568</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1064</v>
+      <c r="B9" t="n">
+        <v>43089</v>
+      </c>
+      <c r="F9" t="n">
+        <v>42407</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33271</v>
+      </c>
+      <c r="N9" t="n">
+        <v>272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8864</v>
+      </c>
+      <c r="V9" t="n">
+        <v>682</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8129264</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>7990659</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>5644431</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>370208</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1976020</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>138605</v>
       </c>
     </row>
     <row r="10">
@@ -1853,23 +1997,41 @@
           <t>202506</t>
         </is>
       </c>
-      <c r="AX10" t="n">
-        <v>58877</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>56997</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>43147</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>621</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>13229</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1880</v>
+      <c r="B10" t="n">
+        <v>57299</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56431</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45067</v>
+      </c>
+      <c r="N10" t="n">
+        <v>419</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10945</v>
+      </c>
+      <c r="V10" t="n">
+        <v>868</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10385897</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10194623</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>7359757</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>352831</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2482035</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>191274</v>
       </c>
     </row>
     <row r="11">
@@ -1878,23 +2040,41 @@
           <t>202505</t>
         </is>
       </c>
-      <c r="AX11" t="n">
-        <v>59150</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>57618</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>43117</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>687</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>13814</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1532</v>
+      <c r="B11" t="n">
+        <v>53438</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52654</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41834</v>
+      </c>
+      <c r="N11" t="n">
+        <v>497</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10323</v>
+      </c>
+      <c r="V11" t="n">
+        <v>784</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9778252</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>9604368</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>7043297</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>469554</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2091517</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>173884</v>
       </c>
     </row>
     <row r="12">
@@ -1903,23 +2083,41 @@
           <t>202504</t>
         </is>
       </c>
-      <c r="AX12" t="n">
-        <v>58125</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>56566</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>42896</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1005</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>12665</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1559</v>
+      <c r="B12" t="n">
+        <v>54744</v>
+      </c>
+      <c r="F12" t="n">
+        <v>53860</v>
+      </c>
+      <c r="J12" t="n">
+        <v>42274</v>
+      </c>
+      <c r="N12" t="n">
+        <v>382</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11204</v>
+      </c>
+      <c r="V12" t="n">
+        <v>884</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9367997</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>9168572</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>6685742</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>309641</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2173189</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>199425</v>
       </c>
     </row>
     <row r="13">
@@ -1928,23 +2126,41 @@
           <t>202503</t>
         </is>
       </c>
-      <c r="AX13" t="n">
-        <v>55304</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>53991</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>40644</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>697</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>12650</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1313</v>
+      <c r="B13" t="n">
+        <v>50562</v>
+      </c>
+      <c r="F13" t="n">
+        <v>49869</v>
+      </c>
+      <c r="J13" t="n">
+        <v>39176</v>
+      </c>
+      <c r="N13" t="n">
+        <v>349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10344</v>
+      </c>
+      <c r="V13" t="n">
+        <v>693</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8620259</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>8295254</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6106866</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>337654</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1850734</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>325005</v>
       </c>
     </row>
   </sheetData>

--- a/docs/hipoteques.xlsx
+++ b/docs/hipoteques.xlsx
@@ -1689,6 +1689,24 @@
       <c r="AT2" t="n">
         <v>327897</v>
       </c>
+      <c r="AX2" t="n">
+        <v>69425</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>67679</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>50582</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>762</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>16335</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1746</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1732,6 +1750,24 @@
       <c r="AT3" t="n">
         <v>197665</v>
       </c>
+      <c r="AX3" t="n">
+        <v>55864</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>54325</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>41522</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>602</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>12201</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1539</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1775,6 +1811,24 @@
       <c r="AT4" t="n">
         <v>167589</v>
       </c>
+      <c r="AX4" t="n">
+        <v>59062</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>57801</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>42888</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>779</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>14134</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1261</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1818,6 +1872,24 @@
       <c r="AT5" t="n">
         <v>270416</v>
       </c>
+      <c r="AX5" t="n">
+        <v>54979</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>53564</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>40101</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>704</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>12759</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1861,6 +1933,24 @@
       <c r="AT6" t="n">
         <v>184846</v>
       </c>
+      <c r="AX6" t="n">
+        <v>62184</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>60663</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>45493</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1173</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>13997</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1521</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1904,6 +1994,24 @@
       <c r="AT7" t="n">
         <v>264761</v>
       </c>
+      <c r="AX7" t="n">
+        <v>67202</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>65643</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>48350</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>829</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>16464</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1559</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1947,6 +2055,24 @@
       <c r="AT8" t="n">
         <v>206482</v>
       </c>
+      <c r="AX8" t="n">
+        <v>52829</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>51315</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>38168</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>875</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>12272</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1514</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1990,6 +2116,24 @@
       <c r="AT9" t="n">
         <v>138605</v>
       </c>
+      <c r="AX9" t="n">
+        <v>40817</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>39753</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>29742</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>443</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>9568</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1064</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2033,6 +2177,24 @@
       <c r="AT10" t="n">
         <v>191274</v>
       </c>
+      <c r="AX10" t="n">
+        <v>58877</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>56997</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>43147</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>621</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>13229</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1880</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2076,6 +2238,24 @@
       <c r="AT11" t="n">
         <v>173884</v>
       </c>
+      <c r="AX11" t="n">
+        <v>59150</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>57618</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>43117</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>687</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>13814</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1532</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2119,6 +2299,24 @@
       <c r="AT12" t="n">
         <v>199425</v>
       </c>
+      <c r="AX12" t="n">
+        <v>58125</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>56566</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>42896</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>12665</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1559</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2161,6 +2359,24 @@
       </c>
       <c r="AT13" t="n">
         <v>325005</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>55304</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>53991</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>40644</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>697</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>12650</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1313</v>
       </c>
     </row>
   </sheetData>

--- a/docs/hipoteques.xlsx
+++ b/docs/hipoteques.xlsx
@@ -684,733 +684,733 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10386</v>
+        <v>7631</v>
       </c>
       <c r="F2" t="n">
-        <v>10340</v>
+        <v>7607</v>
       </c>
       <c r="J2" t="n">
-        <v>8663</v>
+        <v>6310</v>
       </c>
       <c r="N2" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R2" t="n">
-        <v>1631</v>
+        <v>1259</v>
       </c>
       <c r="V2" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>2182497</v>
+        <v>1757921</v>
       </c>
       <c r="AD2" t="n">
-        <v>2171473</v>
+        <v>1570960</v>
       </c>
       <c r="AH2" t="n">
-        <v>1627036</v>
+        <v>1121293</v>
       </c>
       <c r="AL2" t="n">
-        <v>73898</v>
+        <v>23222</v>
       </c>
       <c r="AP2" t="n">
-        <v>470539</v>
+        <v>426445</v>
       </c>
       <c r="AT2" t="n">
-        <v>11024</v>
+        <v>186961</v>
       </c>
       <c r="AX2" t="n">
-        <v>10481</v>
+        <v>7343</v>
       </c>
       <c r="BB2" t="n">
-        <v>10381</v>
+        <v>7249</v>
       </c>
       <c r="BF2" t="n">
-        <v>7908</v>
+        <v>5505</v>
       </c>
       <c r="BJ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1664</v>
+      </c>
+      <c r="BR2" t="n">
         <v>94</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>2379</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10491</v>
+        <v>9268</v>
       </c>
       <c r="F3" t="n">
-        <v>10445</v>
+        <v>9231</v>
       </c>
       <c r="J3" t="n">
-        <v>8556</v>
+        <v>6898</v>
       </c>
       <c r="N3" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="R3" t="n">
-        <v>1835</v>
+        <v>2294</v>
       </c>
       <c r="V3" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Z3" t="n">
-        <v>2117995</v>
+        <v>1614502</v>
       </c>
       <c r="AD3" t="n">
-        <v>2102987</v>
+        <v>1607081</v>
       </c>
       <c r="AH3" t="n">
-        <v>1615565</v>
+        <v>1244137</v>
       </c>
       <c r="AL3" t="n">
-        <v>74862</v>
+        <v>20687</v>
       </c>
       <c r="AP3" t="n">
-        <v>412560</v>
+        <v>342257</v>
       </c>
       <c r="AT3" t="n">
-        <v>15008</v>
+        <v>7421</v>
       </c>
       <c r="AX3" t="n">
-        <v>8277</v>
+        <v>7678</v>
       </c>
       <c r="BB3" t="n">
-        <v>8169</v>
+        <v>7593</v>
       </c>
       <c r="BF3" t="n">
-        <v>6497</v>
+        <v>5778</v>
       </c>
       <c r="BJ3" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="BN3" t="n">
-        <v>1601</v>
+        <v>1751</v>
       </c>
       <c r="BR3" t="n">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8579</v>
+        <v>8720</v>
       </c>
       <c r="F4" t="n">
-        <v>8533</v>
+        <v>8666</v>
       </c>
       <c r="J4" t="n">
-        <v>7213</v>
+        <v>7154</v>
       </c>
       <c r="N4" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>1258</v>
+        <v>1478</v>
       </c>
       <c r="V4" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="Z4" t="n">
-        <v>2146792</v>
+        <v>1761583</v>
       </c>
       <c r="AD4" t="n">
-        <v>2136518</v>
+        <v>1749534</v>
       </c>
       <c r="AH4" t="n">
-        <v>1354701</v>
+        <v>1303546</v>
       </c>
       <c r="AL4" t="n">
-        <v>71516</v>
+        <v>27025</v>
       </c>
       <c r="AP4" t="n">
-        <v>710301</v>
+        <v>418963</v>
       </c>
       <c r="AT4" t="n">
-        <v>10274</v>
+        <v>12049</v>
       </c>
       <c r="AX4" t="n">
-        <v>7832</v>
+        <v>7360</v>
       </c>
       <c r="BB4" t="n">
-        <v>7748</v>
+        <v>7278</v>
       </c>
       <c r="BF4" t="n">
-        <v>5882</v>
+        <v>5696</v>
       </c>
       <c r="BJ4" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="BN4" t="n">
-        <v>1789</v>
+        <v>1516</v>
       </c>
       <c r="BR4" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7916</v>
+        <v>10270</v>
       </c>
       <c r="F5" t="n">
-        <v>7869</v>
+        <v>10232</v>
       </c>
       <c r="J5" t="n">
-        <v>6464</v>
+        <v>8406</v>
       </c>
       <c r="N5" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>1363</v>
+        <v>1791</v>
       </c>
       <c r="V5" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
-        <v>1683968</v>
+        <v>2122808</v>
       </c>
       <c r="AD5" t="n">
-        <v>1668343</v>
+        <v>2112682</v>
       </c>
       <c r="AH5" t="n">
-        <v>1258113</v>
+        <v>1589849</v>
       </c>
       <c r="AL5" t="n">
-        <v>27206</v>
+        <v>22150</v>
       </c>
       <c r="AP5" t="n">
-        <v>383024</v>
+        <v>500683</v>
       </c>
       <c r="AT5" t="n">
-        <v>15625</v>
+        <v>10126</v>
       </c>
       <c r="AX5" t="n">
-        <v>7277</v>
+        <v>8596</v>
       </c>
       <c r="BB5" t="n">
-        <v>7201</v>
+        <v>8506</v>
       </c>
       <c r="BF5" t="n">
-        <v>5489</v>
+        <v>6535</v>
       </c>
       <c r="BJ5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1640</v>
+        <v>1898</v>
       </c>
       <c r="BR5" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8945</v>
+        <v>6957</v>
       </c>
       <c r="F6" t="n">
-        <v>8897</v>
+        <v>6925</v>
       </c>
       <c r="J6" t="n">
-        <v>7373</v>
+        <v>5745</v>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="R6" t="n">
-        <v>1478</v>
+        <v>1145</v>
       </c>
       <c r="V6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
-        <v>1839816</v>
+        <v>1517089</v>
       </c>
       <c r="AD6" t="n">
-        <v>1829251</v>
+        <v>1510300</v>
       </c>
       <c r="AH6" t="n">
-        <v>1386106</v>
+        <v>1084574</v>
       </c>
       <c r="AL6" t="n">
-        <v>35277</v>
+        <v>102172</v>
       </c>
       <c r="AP6" t="n">
-        <v>407868</v>
+        <v>323554</v>
       </c>
       <c r="AT6" t="n">
-        <v>10565</v>
+        <v>6789</v>
       </c>
       <c r="AX6" t="n">
-        <v>8706</v>
+        <v>6216</v>
       </c>
       <c r="BB6" t="n">
-        <v>8630</v>
+        <v>6154</v>
       </c>
       <c r="BF6" t="n">
-        <v>6518</v>
+        <v>4706</v>
       </c>
       <c r="BJ6" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="BN6" t="n">
-        <v>2043</v>
+        <v>1383</v>
       </c>
       <c r="BR6" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10809</v>
+        <v>9759</v>
       </c>
       <c r="F7" t="n">
-        <v>10748</v>
+        <v>9724</v>
       </c>
       <c r="J7" t="n">
-        <v>9025</v>
+        <v>7864</v>
       </c>
       <c r="N7" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="R7" t="n">
-        <v>1666</v>
+        <v>1777</v>
       </c>
       <c r="V7" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2200721</v>
+        <v>2262183</v>
       </c>
       <c r="AD7" t="n">
-        <v>2185933</v>
+        <v>2256685</v>
       </c>
       <c r="AH7" t="n">
-        <v>1714862</v>
+        <v>1469798</v>
       </c>
       <c r="AL7" t="n">
-        <v>81392</v>
+        <v>39586</v>
       </c>
       <c r="AP7" t="n">
-        <v>389679</v>
+        <v>747301</v>
       </c>
       <c r="AT7" t="n">
-        <v>14788</v>
+        <v>5498</v>
       </c>
       <c r="AX7" t="n">
-        <v>10207</v>
+        <v>7023</v>
       </c>
       <c r="BB7" t="n">
-        <v>10110</v>
+        <v>6952</v>
       </c>
       <c r="BF7" t="n">
-        <v>7729</v>
+        <v>5482</v>
       </c>
       <c r="BJ7" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="BN7" t="n">
-        <v>2281</v>
+        <v>1407</v>
       </c>
       <c r="BR7" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9759</v>
+        <v>10809</v>
       </c>
       <c r="F8" t="n">
-        <v>9724</v>
+        <v>10748</v>
       </c>
       <c r="J8" t="n">
-        <v>7864</v>
+        <v>9025</v>
       </c>
       <c r="N8" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="R8" t="n">
-        <v>1777</v>
+        <v>1666</v>
       </c>
       <c r="V8" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="Z8" t="n">
-        <v>2262183</v>
+        <v>2200721</v>
       </c>
       <c r="AD8" t="n">
-        <v>2256685</v>
+        <v>2185933</v>
       </c>
       <c r="AH8" t="n">
-        <v>1469798</v>
+        <v>1714862</v>
       </c>
       <c r="AL8" t="n">
-        <v>39586</v>
+        <v>81392</v>
       </c>
       <c r="AP8" t="n">
-        <v>747301</v>
+        <v>389679</v>
       </c>
       <c r="AT8" t="n">
-        <v>5498</v>
+        <v>14788</v>
       </c>
       <c r="AX8" t="n">
-        <v>7023</v>
+        <v>10207</v>
       </c>
       <c r="BB8" t="n">
-        <v>6952</v>
+        <v>10110</v>
       </c>
       <c r="BF8" t="n">
-        <v>5482</v>
+        <v>7729</v>
       </c>
       <c r="BJ8" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="BN8" t="n">
-        <v>1407</v>
+        <v>2281</v>
       </c>
       <c r="BR8" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6957</v>
+        <v>8945</v>
       </c>
       <c r="F9" t="n">
-        <v>6925</v>
+        <v>8897</v>
       </c>
       <c r="J9" t="n">
-        <v>5745</v>
+        <v>7373</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R9" t="n">
-        <v>1145</v>
+        <v>1478</v>
       </c>
       <c r="V9" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Z9" t="n">
-        <v>1517089</v>
+        <v>1839816</v>
       </c>
       <c r="AD9" t="n">
-        <v>1510300</v>
+        <v>1829251</v>
       </c>
       <c r="AH9" t="n">
-        <v>1084574</v>
+        <v>1386106</v>
       </c>
       <c r="AL9" t="n">
-        <v>102172</v>
+        <v>35277</v>
       </c>
       <c r="AP9" t="n">
-        <v>323554</v>
+        <v>407868</v>
       </c>
       <c r="AT9" t="n">
-        <v>6789</v>
+        <v>10565</v>
       </c>
       <c r="AX9" t="n">
-        <v>6216</v>
+        <v>8706</v>
       </c>
       <c r="BB9" t="n">
-        <v>6154</v>
+        <v>8630</v>
       </c>
       <c r="BF9" t="n">
-        <v>4706</v>
+        <v>6518</v>
       </c>
       <c r="BJ9" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="BN9" t="n">
-        <v>1383</v>
+        <v>2043</v>
       </c>
       <c r="BR9" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10270</v>
+        <v>7916</v>
       </c>
       <c r="F10" t="n">
-        <v>10232</v>
+        <v>7869</v>
       </c>
       <c r="J10" t="n">
-        <v>8406</v>
+        <v>6464</v>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R10" t="n">
-        <v>1791</v>
+        <v>1363</v>
       </c>
       <c r="V10" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Z10" t="n">
-        <v>2122808</v>
+        <v>1683968</v>
       </c>
       <c r="AD10" t="n">
-        <v>2112682</v>
+        <v>1668343</v>
       </c>
       <c r="AH10" t="n">
-        <v>1589849</v>
+        <v>1258113</v>
       </c>
       <c r="AL10" t="n">
-        <v>22150</v>
+        <v>27206</v>
       </c>
       <c r="AP10" t="n">
-        <v>500683</v>
+        <v>383024</v>
       </c>
       <c r="AT10" t="n">
-        <v>10126</v>
+        <v>15625</v>
       </c>
       <c r="AX10" t="n">
-        <v>8596</v>
+        <v>7277</v>
       </c>
       <c r="BB10" t="n">
-        <v>8506</v>
+        <v>7201</v>
       </c>
       <c r="BF10" t="n">
-        <v>6535</v>
+        <v>5489</v>
       </c>
       <c r="BJ10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BN10" t="n">
-        <v>1898</v>
+        <v>1640</v>
       </c>
       <c r="BR10" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8720</v>
+        <v>8579</v>
       </c>
       <c r="F11" t="n">
-        <v>8666</v>
+        <v>8533</v>
       </c>
       <c r="J11" t="n">
-        <v>7154</v>
+        <v>7213</v>
       </c>
       <c r="N11" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>1478</v>
+        <v>1258</v>
       </c>
       <c r="V11" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="Z11" t="n">
-        <v>1761583</v>
+        <v>2146792</v>
       </c>
       <c r="AD11" t="n">
-        <v>1749534</v>
+        <v>2136518</v>
       </c>
       <c r="AH11" t="n">
-        <v>1303546</v>
+        <v>1354701</v>
       </c>
       <c r="AL11" t="n">
-        <v>27025</v>
+        <v>71516</v>
       </c>
       <c r="AP11" t="n">
-        <v>418963</v>
+        <v>710301</v>
       </c>
       <c r="AT11" t="n">
-        <v>12049</v>
+        <v>10274</v>
       </c>
       <c r="AX11" t="n">
-        <v>7360</v>
+        <v>7832</v>
       </c>
       <c r="BB11" t="n">
-        <v>7278</v>
+        <v>7748</v>
       </c>
       <c r="BF11" t="n">
-        <v>5696</v>
+        <v>5882</v>
       </c>
       <c r="BJ11" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="BN11" t="n">
-        <v>1516</v>
+        <v>1789</v>
       </c>
       <c r="BR11" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9268</v>
+        <v>10491</v>
       </c>
       <c r="F12" t="n">
-        <v>9231</v>
+        <v>10445</v>
       </c>
       <c r="J12" t="n">
-        <v>6898</v>
+        <v>8556</v>
       </c>
       <c r="N12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="R12" t="n">
-        <v>2294</v>
+        <v>1835</v>
       </c>
       <c r="V12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Z12" t="n">
-        <v>1614502</v>
+        <v>2117995</v>
       </c>
       <c r="AD12" t="n">
-        <v>1607081</v>
+        <v>2102987</v>
       </c>
       <c r="AH12" t="n">
-        <v>1244137</v>
+        <v>1615565</v>
       </c>
       <c r="AL12" t="n">
-        <v>20687</v>
+        <v>74862</v>
       </c>
       <c r="AP12" t="n">
-        <v>342257</v>
+        <v>412560</v>
       </c>
       <c r="AT12" t="n">
-        <v>7421</v>
+        <v>15008</v>
       </c>
       <c r="AX12" t="n">
-        <v>7678</v>
+        <v>8277</v>
       </c>
       <c r="BB12" t="n">
-        <v>7593</v>
+        <v>8169</v>
       </c>
       <c r="BF12" t="n">
-        <v>5778</v>
+        <v>6497</v>
       </c>
       <c r="BJ12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1751</v>
+        <v>1601</v>
       </c>
       <c r="BR12" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7631</v>
+        <v>10386</v>
       </c>
       <c r="F13" t="n">
-        <v>7607</v>
+        <v>10340</v>
       </c>
       <c r="J13" t="n">
-        <v>6310</v>
+        <v>8663</v>
       </c>
       <c r="N13" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R13" t="n">
-        <v>1259</v>
+        <v>1631</v>
       </c>
       <c r="V13" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Z13" t="n">
-        <v>1757921</v>
+        <v>2182497</v>
       </c>
       <c r="AD13" t="n">
-        <v>1570960</v>
+        <v>2171473</v>
       </c>
       <c r="AH13" t="n">
-        <v>1121293</v>
+        <v>1627036</v>
       </c>
       <c r="AL13" t="n">
-        <v>23222</v>
+        <v>73898</v>
       </c>
       <c r="AP13" t="n">
-        <v>426445</v>
+        <v>470539</v>
       </c>
       <c r="AT13" t="n">
-        <v>186961</v>
+        <v>11024</v>
       </c>
       <c r="AX13" t="n">
-        <v>7343</v>
+        <v>10481</v>
       </c>
       <c r="BB13" t="n">
-        <v>7249</v>
+        <v>10381</v>
       </c>
       <c r="BF13" t="n">
-        <v>5505</v>
+        <v>7908</v>
       </c>
       <c r="BJ13" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="BN13" t="n">
-        <v>1664</v>
+        <v>2379</v>
       </c>
       <c r="BR13" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1650,733 +1650,733 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59531</v>
+        <v>50562</v>
       </c>
       <c r="F2" t="n">
-        <v>58459</v>
+        <v>49869</v>
       </c>
       <c r="J2" t="n">
-        <v>46661</v>
+        <v>39176</v>
       </c>
       <c r="N2" t="n">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="R2" t="n">
-        <v>11340</v>
+        <v>10344</v>
       </c>
       <c r="V2" t="n">
-        <v>1072</v>
+        <v>693</v>
       </c>
       <c r="Z2" t="n">
-        <v>11478708</v>
+        <v>8620259</v>
       </c>
       <c r="AD2" t="n">
-        <v>11150811</v>
+        <v>8295254</v>
       </c>
       <c r="AH2" t="n">
-        <v>8125195</v>
+        <v>6106866</v>
       </c>
       <c r="AL2" t="n">
-        <v>408039</v>
+        <v>337654</v>
       </c>
       <c r="AP2" t="n">
-        <v>2617577</v>
+        <v>1850734</v>
       </c>
       <c r="AT2" t="n">
-        <v>327897</v>
+        <v>325005</v>
       </c>
       <c r="AX2" t="n">
-        <v>69425</v>
+        <v>55304</v>
       </c>
       <c r="BB2" t="n">
-        <v>67679</v>
+        <v>53991</v>
       </c>
       <c r="BF2" t="n">
-        <v>50582</v>
+        <v>40644</v>
       </c>
       <c r="BJ2" t="n">
-        <v>762</v>
+        <v>697</v>
       </c>
       <c r="BN2" t="n">
-        <v>16335</v>
+        <v>12650</v>
       </c>
       <c r="BR2" t="n">
-        <v>1746</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59349</v>
+        <v>54744</v>
       </c>
       <c r="F3" t="n">
-        <v>58406</v>
+        <v>53860</v>
       </c>
       <c r="J3" t="n">
-        <v>45563</v>
+        <v>42274</v>
       </c>
       <c r="N3" t="n">
-        <v>507</v>
+        <v>382</v>
       </c>
       <c r="R3" t="n">
-        <v>12336</v>
+        <v>11204</v>
       </c>
       <c r="V3" t="n">
-        <v>943</v>
+        <v>884</v>
       </c>
       <c r="Z3" t="n">
-        <v>11181160</v>
+        <v>9367997</v>
       </c>
       <c r="AD3" t="n">
-        <v>10983495</v>
+        <v>9168572</v>
       </c>
       <c r="AH3" t="n">
-        <v>7895166</v>
+        <v>6685742</v>
       </c>
       <c r="AL3" t="n">
-        <v>477874</v>
+        <v>309641</v>
       </c>
       <c r="AP3" t="n">
-        <v>2610455</v>
+        <v>2173189</v>
       </c>
       <c r="AT3" t="n">
-        <v>197665</v>
+        <v>199425</v>
       </c>
       <c r="AX3" t="n">
-        <v>55864</v>
+        <v>58125</v>
       </c>
       <c r="BB3" t="n">
-        <v>54325</v>
+        <v>56566</v>
       </c>
       <c r="BF3" t="n">
-        <v>41522</v>
+        <v>42896</v>
       </c>
       <c r="BJ3" t="n">
-        <v>602</v>
+        <v>1005</v>
       </c>
       <c r="BN3" t="n">
-        <v>12201</v>
+        <v>12665</v>
       </c>
       <c r="BR3" t="n">
-        <v>1539</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49384</v>
+        <v>53438</v>
       </c>
       <c r="F4" t="n">
-        <v>48585</v>
+        <v>52654</v>
       </c>
       <c r="J4" t="n">
-        <v>39330</v>
+        <v>41834</v>
       </c>
       <c r="N4" t="n">
-        <v>404</v>
+        <v>497</v>
       </c>
       <c r="R4" t="n">
-        <v>8851</v>
+        <v>10323</v>
       </c>
       <c r="V4" t="n">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="Z4" t="n">
-        <v>9949811</v>
+        <v>9778252</v>
       </c>
       <c r="AD4" t="n">
-        <v>9782222</v>
+        <v>9604368</v>
       </c>
       <c r="AH4" t="n">
-        <v>6665198</v>
+        <v>7043297</v>
       </c>
       <c r="AL4" t="n">
-        <v>424379</v>
+        <v>469554</v>
       </c>
       <c r="AP4" t="n">
-        <v>2692645</v>
+        <v>2091517</v>
       </c>
       <c r="AT4" t="n">
-        <v>167589</v>
+        <v>173884</v>
       </c>
       <c r="AX4" t="n">
-        <v>59062</v>
+        <v>59150</v>
       </c>
       <c r="BB4" t="n">
-        <v>57801</v>
+        <v>57618</v>
       </c>
       <c r="BF4" t="n">
-        <v>42888</v>
+        <v>43117</v>
       </c>
       <c r="BJ4" t="n">
-        <v>779</v>
+        <v>687</v>
       </c>
       <c r="BN4" t="n">
-        <v>14134</v>
+        <v>13814</v>
       </c>
       <c r="BR4" t="n">
-        <v>1261</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49271</v>
+        <v>57299</v>
       </c>
       <c r="F5" t="n">
-        <v>48290</v>
+        <v>56431</v>
       </c>
       <c r="J5" t="n">
-        <v>37841</v>
+        <v>45067</v>
       </c>
       <c r="N5" t="n">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="R5" t="n">
-        <v>9962</v>
+        <v>10945</v>
       </c>
       <c r="V5" t="n">
-        <v>981</v>
+        <v>868</v>
       </c>
       <c r="Z5" t="n">
-        <v>9878599</v>
+        <v>10385897</v>
       </c>
       <c r="AD5" t="n">
-        <v>9608183</v>
+        <v>10194623</v>
       </c>
       <c r="AH5" t="n">
-        <v>6528887</v>
+        <v>7359757</v>
       </c>
       <c r="AL5" t="n">
-        <v>545099</v>
+        <v>352831</v>
       </c>
       <c r="AP5" t="n">
-        <v>2534197</v>
+        <v>2482035</v>
       </c>
       <c r="AT5" t="n">
-        <v>270416</v>
+        <v>191274</v>
       </c>
       <c r="AX5" t="n">
-        <v>54979</v>
+        <v>58877</v>
       </c>
       <c r="BB5" t="n">
-        <v>53564</v>
+        <v>56997</v>
       </c>
       <c r="BF5" t="n">
-        <v>40101</v>
+        <v>43147</v>
       </c>
       <c r="BJ5" t="n">
-        <v>704</v>
+        <v>621</v>
       </c>
       <c r="BN5" t="n">
-        <v>12759</v>
+        <v>13229</v>
       </c>
       <c r="BR5" t="n">
-        <v>1415</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55762</v>
+        <v>43089</v>
       </c>
       <c r="F6" t="n">
-        <v>54928</v>
+        <v>42407</v>
       </c>
       <c r="J6" t="n">
-        <v>43319</v>
+        <v>33271</v>
       </c>
       <c r="N6" t="n">
-        <v>368</v>
+        <v>272</v>
       </c>
       <c r="R6" t="n">
-        <v>11241</v>
+        <v>8864</v>
       </c>
       <c r="V6" t="n">
-        <v>834</v>
+        <v>682</v>
       </c>
       <c r="Z6" t="n">
-        <v>10695781</v>
+        <v>8129264</v>
       </c>
       <c r="AD6" t="n">
-        <v>10510935</v>
+        <v>7990659</v>
       </c>
       <c r="AH6" t="n">
-        <v>7397618</v>
+        <v>5644431</v>
       </c>
       <c r="AL6" t="n">
-        <v>265620</v>
+        <v>370208</v>
       </c>
       <c r="AP6" t="n">
-        <v>2847697</v>
+        <v>1976020</v>
       </c>
       <c r="AT6" t="n">
-        <v>184846</v>
+        <v>138605</v>
       </c>
       <c r="AX6" t="n">
-        <v>62184</v>
+        <v>40817</v>
       </c>
       <c r="BB6" t="n">
-        <v>60663</v>
+        <v>39753</v>
       </c>
       <c r="BF6" t="n">
-        <v>45493</v>
+        <v>29742</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1173</v>
+        <v>443</v>
       </c>
       <c r="BN6" t="n">
-        <v>13997</v>
+        <v>9568</v>
       </c>
       <c r="BR6" t="n">
-        <v>1521</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66960</v>
+        <v>59261</v>
       </c>
       <c r="F7" t="n">
-        <v>65863</v>
+        <v>58227</v>
       </c>
       <c r="J7" t="n">
-        <v>52198</v>
+        <v>46120</v>
       </c>
       <c r="N7" t="n">
-        <v>367</v>
+        <v>479</v>
       </c>
       <c r="R7" t="n">
-        <v>13298</v>
+        <v>11628</v>
       </c>
       <c r="V7" t="n">
-        <v>1097</v>
+        <v>1034</v>
       </c>
       <c r="Z7" t="n">
-        <v>12252940</v>
+        <v>11566816</v>
       </c>
       <c r="AD7" t="n">
-        <v>11988179</v>
+        <v>11360334</v>
       </c>
       <c r="AH7" t="n">
-        <v>8721246</v>
+        <v>7914755</v>
       </c>
       <c r="AL7" t="n">
-        <v>443243</v>
+        <v>528921</v>
       </c>
       <c r="AP7" t="n">
-        <v>2823690</v>
+        <v>2916658</v>
       </c>
       <c r="AT7" t="n">
-        <v>264761</v>
+        <v>206482</v>
       </c>
       <c r="AX7" t="n">
-        <v>67202</v>
+        <v>52829</v>
       </c>
       <c r="BB7" t="n">
-        <v>65643</v>
+        <v>51315</v>
       </c>
       <c r="BF7" t="n">
-        <v>48350</v>
+        <v>38168</v>
       </c>
       <c r="BJ7" t="n">
-        <v>829</v>
+        <v>875</v>
       </c>
       <c r="BN7" t="n">
-        <v>16464</v>
+        <v>12272</v>
       </c>
       <c r="BR7" t="n">
-        <v>1559</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59261</v>
+        <v>66960</v>
       </c>
       <c r="F8" t="n">
-        <v>58227</v>
+        <v>65863</v>
       </c>
       <c r="J8" t="n">
-        <v>46120</v>
+        <v>52198</v>
       </c>
       <c r="N8" t="n">
-        <v>479</v>
+        <v>367</v>
       </c>
       <c r="R8" t="n">
-        <v>11628</v>
+        <v>13298</v>
       </c>
       <c r="V8" t="n">
-        <v>1034</v>
+        <v>1097</v>
       </c>
       <c r="Z8" t="n">
-        <v>11566816</v>
+        <v>12252940</v>
       </c>
       <c r="AD8" t="n">
-        <v>11360334</v>
+        <v>11988179</v>
       </c>
       <c r="AH8" t="n">
-        <v>7914755</v>
+        <v>8721246</v>
       </c>
       <c r="AL8" t="n">
-        <v>528921</v>
+        <v>443243</v>
       </c>
       <c r="AP8" t="n">
-        <v>2916658</v>
+        <v>2823690</v>
       </c>
       <c r="AT8" t="n">
-        <v>206482</v>
+        <v>264761</v>
       </c>
       <c r="AX8" t="n">
-        <v>52829</v>
+        <v>67202</v>
       </c>
       <c r="BB8" t="n">
-        <v>51315</v>
+        <v>65643</v>
       </c>
       <c r="BF8" t="n">
-        <v>38168</v>
+        <v>48350</v>
       </c>
       <c r="BJ8" t="n">
-        <v>875</v>
+        <v>829</v>
       </c>
       <c r="BN8" t="n">
-        <v>12272</v>
+        <v>16464</v>
       </c>
       <c r="BR8" t="n">
-        <v>1514</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43089</v>
+        <v>55762</v>
       </c>
       <c r="F9" t="n">
-        <v>42407</v>
+        <v>54928</v>
       </c>
       <c r="J9" t="n">
-        <v>33271</v>
+        <v>43319</v>
       </c>
       <c r="N9" t="n">
-        <v>272</v>
+        <v>368</v>
       </c>
       <c r="R9" t="n">
-        <v>8864</v>
+        <v>11241</v>
       </c>
       <c r="V9" t="n">
-        <v>682</v>
+        <v>834</v>
       </c>
       <c r="Z9" t="n">
-        <v>8129264</v>
+        <v>10695781</v>
       </c>
       <c r="AD9" t="n">
-        <v>7990659</v>
+        <v>10510935</v>
       </c>
       <c r="AH9" t="n">
-        <v>5644431</v>
+        <v>7397618</v>
       </c>
       <c r="AL9" t="n">
-        <v>370208</v>
+        <v>265620</v>
       </c>
       <c r="AP9" t="n">
-        <v>1976020</v>
+        <v>2847697</v>
       </c>
       <c r="AT9" t="n">
-        <v>138605</v>
+        <v>184846</v>
       </c>
       <c r="AX9" t="n">
-        <v>40817</v>
+        <v>62184</v>
       </c>
       <c r="BB9" t="n">
-        <v>39753</v>
+        <v>60663</v>
       </c>
       <c r="BF9" t="n">
-        <v>29742</v>
+        <v>45493</v>
       </c>
       <c r="BJ9" t="n">
-        <v>443</v>
+        <v>1173</v>
       </c>
       <c r="BN9" t="n">
-        <v>9568</v>
+        <v>13997</v>
       </c>
       <c r="BR9" t="n">
-        <v>1064</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57299</v>
+        <v>49271</v>
       </c>
       <c r="F10" t="n">
-        <v>56431</v>
+        <v>48290</v>
       </c>
       <c r="J10" t="n">
-        <v>45067</v>
+        <v>37841</v>
       </c>
       <c r="N10" t="n">
-        <v>419</v>
+        <v>487</v>
       </c>
       <c r="R10" t="n">
-        <v>10945</v>
+        <v>9962</v>
       </c>
       <c r="V10" t="n">
-        <v>868</v>
+        <v>981</v>
       </c>
       <c r="Z10" t="n">
-        <v>10385897</v>
+        <v>9878599</v>
       </c>
       <c r="AD10" t="n">
-        <v>10194623</v>
+        <v>9608183</v>
       </c>
       <c r="AH10" t="n">
-        <v>7359757</v>
+        <v>6528887</v>
       </c>
       <c r="AL10" t="n">
-        <v>352831</v>
+        <v>545099</v>
       </c>
       <c r="AP10" t="n">
-        <v>2482035</v>
+        <v>2534197</v>
       </c>
       <c r="AT10" t="n">
-        <v>191274</v>
+        <v>270416</v>
       </c>
       <c r="AX10" t="n">
-        <v>58877</v>
+        <v>54979</v>
       </c>
       <c r="BB10" t="n">
-        <v>56997</v>
+        <v>53564</v>
       </c>
       <c r="BF10" t="n">
-        <v>43147</v>
+        <v>40101</v>
       </c>
       <c r="BJ10" t="n">
-        <v>621</v>
+        <v>704</v>
       </c>
       <c r="BN10" t="n">
-        <v>13229</v>
+        <v>12759</v>
       </c>
       <c r="BR10" t="n">
-        <v>1880</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53438</v>
+        <v>49384</v>
       </c>
       <c r="F11" t="n">
-        <v>52654</v>
+        <v>48585</v>
       </c>
       <c r="J11" t="n">
-        <v>41834</v>
+        <v>39330</v>
       </c>
       <c r="N11" t="n">
-        <v>497</v>
+        <v>404</v>
       </c>
       <c r="R11" t="n">
-        <v>10323</v>
+        <v>8851</v>
       </c>
       <c r="V11" t="n">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="Z11" t="n">
-        <v>9778252</v>
+        <v>9949811</v>
       </c>
       <c r="AD11" t="n">
-        <v>9604368</v>
+        <v>9782222</v>
       </c>
       <c r="AH11" t="n">
-        <v>7043297</v>
+        <v>6665198</v>
       </c>
       <c r="AL11" t="n">
-        <v>469554</v>
+        <v>424379</v>
       </c>
       <c r="AP11" t="n">
-        <v>2091517</v>
+        <v>2692645</v>
       </c>
       <c r="AT11" t="n">
-        <v>173884</v>
+        <v>167589</v>
       </c>
       <c r="AX11" t="n">
-        <v>59150</v>
+        <v>59062</v>
       </c>
       <c r="BB11" t="n">
-        <v>57618</v>
+        <v>57801</v>
       </c>
       <c r="BF11" t="n">
-        <v>43117</v>
+        <v>42888</v>
       </c>
       <c r="BJ11" t="n">
-        <v>687</v>
+        <v>779</v>
       </c>
       <c r="BN11" t="n">
-        <v>13814</v>
+        <v>14134</v>
       </c>
       <c r="BR11" t="n">
-        <v>1532</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54744</v>
+        <v>59349</v>
       </c>
       <c r="F12" t="n">
-        <v>53860</v>
+        <v>58406</v>
       </c>
       <c r="J12" t="n">
-        <v>42274</v>
+        <v>45563</v>
       </c>
       <c r="N12" t="n">
-        <v>382</v>
+        <v>507</v>
       </c>
       <c r="R12" t="n">
-        <v>11204</v>
+        <v>12336</v>
       </c>
       <c r="V12" t="n">
-        <v>884</v>
+        <v>943</v>
       </c>
       <c r="Z12" t="n">
-        <v>9367997</v>
+        <v>11181160</v>
       </c>
       <c r="AD12" t="n">
-        <v>9168572</v>
+        <v>10983495</v>
       </c>
       <c r="AH12" t="n">
-        <v>6685742</v>
+        <v>7895166</v>
       </c>
       <c r="AL12" t="n">
-        <v>309641</v>
+        <v>477874</v>
       </c>
       <c r="AP12" t="n">
-        <v>2173189</v>
+        <v>2610455</v>
       </c>
       <c r="AT12" t="n">
-        <v>199425</v>
+        <v>197665</v>
       </c>
       <c r="AX12" t="n">
-        <v>58125</v>
+        <v>55864</v>
       </c>
       <c r="BB12" t="n">
-        <v>56566</v>
+        <v>54325</v>
       </c>
       <c r="BF12" t="n">
-        <v>42896</v>
+        <v>41522</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1005</v>
+        <v>602</v>
       </c>
       <c r="BN12" t="n">
-        <v>12665</v>
+        <v>12201</v>
       </c>
       <c r="BR12" t="n">
-        <v>1559</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50562</v>
+        <v>59531</v>
       </c>
       <c r="F13" t="n">
-        <v>49869</v>
+        <v>58459</v>
       </c>
       <c r="J13" t="n">
-        <v>39176</v>
+        <v>46661</v>
       </c>
       <c r="N13" t="n">
-        <v>349</v>
+        <v>458</v>
       </c>
       <c r="R13" t="n">
-        <v>10344</v>
+        <v>11340</v>
       </c>
       <c r="V13" t="n">
-        <v>693</v>
+        <v>1072</v>
       </c>
       <c r="Z13" t="n">
-        <v>8620259</v>
+        <v>11478708</v>
       </c>
       <c r="AD13" t="n">
-        <v>8295254</v>
+        <v>11150811</v>
       </c>
       <c r="AH13" t="n">
-        <v>6106866</v>
+        <v>8125195</v>
       </c>
       <c r="AL13" t="n">
-        <v>337654</v>
+        <v>408039</v>
       </c>
       <c r="AP13" t="n">
-        <v>1850734</v>
+        <v>2617577</v>
       </c>
       <c r="AT13" t="n">
-        <v>325005</v>
+        <v>327897</v>
       </c>
       <c r="AX13" t="n">
-        <v>55304</v>
+        <v>69425</v>
       </c>
       <c r="BB13" t="n">
-        <v>53991</v>
+        <v>67679</v>
       </c>
       <c r="BF13" t="n">
-        <v>40644</v>
+        <v>50582</v>
       </c>
       <c r="BJ13" t="n">
-        <v>697</v>
+        <v>762</v>
       </c>
       <c r="BN13" t="n">
-        <v>12650</v>
+        <v>16335</v>
       </c>
       <c r="BR13" t="n">
-        <v>1313</v>
+        <v>1746</v>
       </c>
     </row>
   </sheetData>

--- a/docs/hipoteques.xlsx
+++ b/docs/hipoteques.xlsx
@@ -684,7 +684,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -745,7 +745,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -806,7 +806,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -928,7 +928,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -989,7 +989,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1050,7 +1050,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1111,7 +1111,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1172,7 +1172,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1233,7 +1233,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1294,7 +1294,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1355,7 +1355,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1650,7 +1650,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1711,7 +1711,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1772,7 +1772,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1833,7 +1833,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1894,7 +1894,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1955,7 +1955,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2016,7 +2016,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2077,7 +2077,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2138,7 +2138,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2199,7 +2199,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2260,7 +2260,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2321,7 +2321,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B13" t="n">

--- a/docs/hipoteques.xlsx
+++ b/docs/hipoteques.xlsx
@@ -684,486 +684,486 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7631</v>
+        <v>9268</v>
       </c>
       <c r="F2" t="n">
-        <v>7607</v>
+        <v>9231</v>
       </c>
       <c r="J2" t="n">
-        <v>6310</v>
+        <v>6898</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" t="n">
-        <v>1259</v>
+        <v>2294</v>
       </c>
       <c r="V2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="Z2" t="n">
-        <v>1757921</v>
+        <v>1614502</v>
       </c>
       <c r="AD2" t="n">
-        <v>1570960</v>
+        <v>1607081</v>
       </c>
       <c r="AH2" t="n">
-        <v>1121293</v>
+        <v>1244137</v>
       </c>
       <c r="AL2" t="n">
-        <v>23222</v>
+        <v>20687</v>
       </c>
       <c r="AP2" t="n">
-        <v>426445</v>
+        <v>342257</v>
       </c>
       <c r="AT2" t="n">
-        <v>186961</v>
+        <v>7421</v>
       </c>
       <c r="AX2" t="n">
-        <v>7343</v>
+        <v>7678</v>
       </c>
       <c r="BB2" t="n">
-        <v>7249</v>
+        <v>7593</v>
       </c>
       <c r="BF2" t="n">
-        <v>5505</v>
+        <v>5778</v>
       </c>
       <c r="BJ2" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="BN2" t="n">
-        <v>1664</v>
+        <v>1751</v>
       </c>
       <c r="BR2" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9268</v>
+        <v>8720</v>
       </c>
       <c r="F3" t="n">
-        <v>9231</v>
+        <v>8666</v>
       </c>
       <c r="J3" t="n">
-        <v>6898</v>
+        <v>7154</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R3" t="n">
-        <v>2294</v>
+        <v>1478</v>
       </c>
       <c r="V3" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="Z3" t="n">
-        <v>1614502</v>
+        <v>1761583</v>
       </c>
       <c r="AD3" t="n">
-        <v>1607081</v>
+        <v>1749534</v>
       </c>
       <c r="AH3" t="n">
-        <v>1244137</v>
+        <v>1303546</v>
       </c>
       <c r="AL3" t="n">
-        <v>20687</v>
+        <v>27025</v>
       </c>
       <c r="AP3" t="n">
-        <v>342257</v>
+        <v>418963</v>
       </c>
       <c r="AT3" t="n">
-        <v>7421</v>
+        <v>12049</v>
       </c>
       <c r="AX3" t="n">
-        <v>7678</v>
+        <v>7360</v>
       </c>
       <c r="BB3" t="n">
-        <v>7593</v>
+        <v>7278</v>
       </c>
       <c r="BF3" t="n">
-        <v>5778</v>
+        <v>5696</v>
       </c>
       <c r="BJ3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BN3" t="n">
-        <v>1751</v>
+        <v>1516</v>
       </c>
       <c r="BR3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8720</v>
+        <v>10270</v>
       </c>
       <c r="F4" t="n">
-        <v>8666</v>
+        <v>10232</v>
       </c>
       <c r="J4" t="n">
-        <v>7154</v>
+        <v>8406</v>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
-        <v>1478</v>
+        <v>1791</v>
       </c>
       <c r="V4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>1761583</v>
+        <v>2122808</v>
       </c>
       <c r="AD4" t="n">
-        <v>1749534</v>
+        <v>2112682</v>
       </c>
       <c r="AH4" t="n">
-        <v>1303546</v>
+        <v>1589849</v>
       </c>
       <c r="AL4" t="n">
-        <v>27025</v>
+        <v>22150</v>
       </c>
       <c r="AP4" t="n">
-        <v>418963</v>
+        <v>500683</v>
       </c>
       <c r="AT4" t="n">
-        <v>12049</v>
+        <v>10126</v>
       </c>
       <c r="AX4" t="n">
-        <v>7360</v>
+        <v>8596</v>
       </c>
       <c r="BB4" t="n">
-        <v>7278</v>
+        <v>8506</v>
       </c>
       <c r="BF4" t="n">
-        <v>5696</v>
+        <v>6535</v>
       </c>
       <c r="BJ4" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1516</v>
+        <v>1898</v>
       </c>
       <c r="BR4" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10270</v>
+        <v>6957</v>
       </c>
       <c r="F5" t="n">
-        <v>10232</v>
+        <v>6925</v>
       </c>
       <c r="J5" t="n">
-        <v>8406</v>
+        <v>5745</v>
       </c>
       <c r="N5" t="n">
         <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>1791</v>
+        <v>1145</v>
       </c>
       <c r="V5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>2122808</v>
+        <v>1517089</v>
       </c>
       <c r="AD5" t="n">
-        <v>2112682</v>
+        <v>1510300</v>
       </c>
       <c r="AH5" t="n">
-        <v>1589849</v>
+        <v>1084574</v>
       </c>
       <c r="AL5" t="n">
-        <v>22150</v>
+        <v>102172</v>
       </c>
       <c r="AP5" t="n">
-        <v>500683</v>
+        <v>323554</v>
       </c>
       <c r="AT5" t="n">
-        <v>10126</v>
+        <v>6789</v>
       </c>
       <c r="AX5" t="n">
-        <v>8596</v>
+        <v>6216</v>
       </c>
       <c r="BB5" t="n">
-        <v>8506</v>
+        <v>6154</v>
       </c>
       <c r="BF5" t="n">
-        <v>6535</v>
+        <v>4706</v>
       </c>
       <c r="BJ5" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1898</v>
+        <v>1383</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6957</v>
+        <v>9759</v>
       </c>
       <c r="F6" t="n">
-        <v>6925</v>
+        <v>9724</v>
       </c>
       <c r="J6" t="n">
-        <v>5745</v>
+        <v>7864</v>
       </c>
       <c r="N6" t="n">
+        <v>83</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1777</v>
+      </c>
+      <c r="V6" t="n">
         <v>35</v>
       </c>
-      <c r="R6" t="n">
-        <v>1145</v>
-      </c>
-      <c r="V6" t="n">
-        <v>32</v>
-      </c>
       <c r="Z6" t="n">
-        <v>1517089</v>
+        <v>2262183</v>
       </c>
       <c r="AD6" t="n">
-        <v>1510300</v>
+        <v>2256685</v>
       </c>
       <c r="AH6" t="n">
-        <v>1084574</v>
+        <v>1469798</v>
       </c>
       <c r="AL6" t="n">
-        <v>102172</v>
+        <v>39586</v>
       </c>
       <c r="AP6" t="n">
-        <v>323554</v>
+        <v>747301</v>
       </c>
       <c r="AT6" t="n">
-        <v>6789</v>
+        <v>5498</v>
       </c>
       <c r="AX6" t="n">
-        <v>6216</v>
+        <v>7023</v>
       </c>
       <c r="BB6" t="n">
-        <v>6154</v>
+        <v>6952</v>
       </c>
       <c r="BF6" t="n">
-        <v>4706</v>
+        <v>5482</v>
       </c>
       <c r="BJ6" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="BN6" t="n">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="BR6" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9759</v>
+        <v>10809</v>
       </c>
       <c r="F7" t="n">
-        <v>9724</v>
+        <v>10748</v>
       </c>
       <c r="J7" t="n">
-        <v>7864</v>
+        <v>9025</v>
       </c>
       <c r="N7" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="R7" t="n">
-        <v>1777</v>
+        <v>1666</v>
       </c>
       <c r="V7" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="Z7" t="n">
-        <v>2262183</v>
+        <v>2200721</v>
       </c>
       <c r="AD7" t="n">
-        <v>2256685</v>
+        <v>2185933</v>
       </c>
       <c r="AH7" t="n">
-        <v>1469798</v>
+        <v>1714862</v>
       </c>
       <c r="AL7" t="n">
-        <v>39586</v>
+        <v>81392</v>
       </c>
       <c r="AP7" t="n">
-        <v>747301</v>
+        <v>389679</v>
       </c>
       <c r="AT7" t="n">
-        <v>5498</v>
+        <v>14788</v>
       </c>
       <c r="AX7" t="n">
-        <v>7023</v>
+        <v>10207</v>
       </c>
       <c r="BB7" t="n">
-        <v>6952</v>
+        <v>10110</v>
       </c>
       <c r="BF7" t="n">
-        <v>5482</v>
+        <v>7729</v>
       </c>
       <c r="BJ7" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="BN7" t="n">
-        <v>1407</v>
+        <v>2281</v>
       </c>
       <c r="BR7" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10809</v>
+        <v>8945</v>
       </c>
       <c r="F8" t="n">
-        <v>10748</v>
+        <v>8897</v>
       </c>
       <c r="J8" t="n">
-        <v>9025</v>
+        <v>7373</v>
       </c>
       <c r="N8" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>1666</v>
+        <v>1478</v>
       </c>
       <c r="V8" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="Z8" t="n">
-        <v>2200721</v>
+        <v>1839816</v>
       </c>
       <c r="AD8" t="n">
-        <v>2185933</v>
+        <v>1829251</v>
       </c>
       <c r="AH8" t="n">
-        <v>1714862</v>
+        <v>1386106</v>
       </c>
       <c r="AL8" t="n">
-        <v>81392</v>
+        <v>35277</v>
       </c>
       <c r="AP8" t="n">
-        <v>389679</v>
+        <v>407868</v>
       </c>
       <c r="AT8" t="n">
-        <v>14788</v>
+        <v>10565</v>
       </c>
       <c r="AX8" t="n">
-        <v>10207</v>
+        <v>8706</v>
       </c>
       <c r="BB8" t="n">
-        <v>10110</v>
+        <v>8630</v>
       </c>
       <c r="BF8" t="n">
-        <v>7729</v>
+        <v>6518</v>
       </c>
       <c r="BJ8" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="BN8" t="n">
-        <v>2281</v>
+        <v>2043</v>
       </c>
       <c r="BR8" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8945</v>
+        <v>7916</v>
       </c>
       <c r="F9" t="n">
-        <v>8897</v>
+        <v>7869</v>
       </c>
       <c r="J9" t="n">
-        <v>7373</v>
+        <v>6464</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R9" t="n">
-        <v>1478</v>
+        <v>1363</v>
       </c>
       <c r="V9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z9" t="n">
-        <v>1839816</v>
+        <v>1683968</v>
       </c>
       <c r="AD9" t="n">
-        <v>1829251</v>
+        <v>1668343</v>
       </c>
       <c r="AH9" t="n">
-        <v>1386106</v>
+        <v>1258113</v>
       </c>
       <c r="AL9" t="n">
-        <v>35277</v>
+        <v>27206</v>
       </c>
       <c r="AP9" t="n">
-        <v>407868</v>
+        <v>383024</v>
       </c>
       <c r="AT9" t="n">
-        <v>10565</v>
+        <v>15625</v>
       </c>
       <c r="AX9" t="n">
-        <v>8706</v>
+        <v>7277</v>
       </c>
       <c r="BB9" t="n">
-        <v>8630</v>
+        <v>7201</v>
       </c>
       <c r="BF9" t="n">
-        <v>6518</v>
+        <v>5489</v>
       </c>
       <c r="BJ9" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="BN9" t="n">
-        <v>2043</v>
+        <v>1640</v>
       </c>
       <c r="BR9" t="n">
         <v>76</v>
@@ -1172,245 +1172,245 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7916</v>
+        <v>8579</v>
       </c>
       <c r="F10" t="n">
-        <v>7869</v>
+        <v>8533</v>
       </c>
       <c r="J10" t="n">
-        <v>6464</v>
+        <v>7213</v>
       </c>
       <c r="N10" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>1363</v>
+        <v>1258</v>
       </c>
       <c r="V10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z10" t="n">
-        <v>1683968</v>
+        <v>2146792</v>
       </c>
       <c r="AD10" t="n">
-        <v>1668343</v>
+        <v>2136518</v>
       </c>
       <c r="AH10" t="n">
-        <v>1258113</v>
+        <v>1354701</v>
       </c>
       <c r="AL10" t="n">
-        <v>27206</v>
+        <v>71516</v>
       </c>
       <c r="AP10" t="n">
-        <v>383024</v>
+        <v>710301</v>
       </c>
       <c r="AT10" t="n">
-        <v>15625</v>
+        <v>10274</v>
       </c>
       <c r="AX10" t="n">
-        <v>7277</v>
+        <v>7832</v>
       </c>
       <c r="BB10" t="n">
-        <v>7201</v>
+        <v>7748</v>
       </c>
       <c r="BF10" t="n">
-        <v>5489</v>
+        <v>5882</v>
       </c>
       <c r="BJ10" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="BN10" t="n">
-        <v>1640</v>
+        <v>1789</v>
       </c>
       <c r="BR10" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8579</v>
+        <v>10491</v>
       </c>
       <c r="F11" t="n">
-        <v>8533</v>
+        <v>10445</v>
       </c>
       <c r="J11" t="n">
-        <v>7213</v>
+        <v>8556</v>
       </c>
       <c r="N11" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="R11" t="n">
-        <v>1258</v>
+        <v>1835</v>
       </c>
       <c r="V11" t="n">
         <v>46</v>
       </c>
       <c r="Z11" t="n">
-        <v>2146792</v>
+        <v>2117995</v>
       </c>
       <c r="AD11" t="n">
-        <v>2136518</v>
+        <v>2102987</v>
       </c>
       <c r="AH11" t="n">
-        <v>1354701</v>
+        <v>1615565</v>
       </c>
       <c r="AL11" t="n">
-        <v>71516</v>
+        <v>74862</v>
       </c>
       <c r="AP11" t="n">
-        <v>710301</v>
+        <v>412560</v>
       </c>
       <c r="AT11" t="n">
-        <v>10274</v>
+        <v>15008</v>
       </c>
       <c r="AX11" t="n">
-        <v>7832</v>
+        <v>8277</v>
       </c>
       <c r="BB11" t="n">
-        <v>7748</v>
+        <v>8169</v>
       </c>
       <c r="BF11" t="n">
-        <v>5882</v>
+        <v>6497</v>
       </c>
       <c r="BJ11" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="BN11" t="n">
-        <v>1789</v>
+        <v>1601</v>
       </c>
       <c r="BR11" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10491</v>
+        <v>10386</v>
       </c>
       <c r="F12" t="n">
-        <v>10445</v>
+        <v>10340</v>
       </c>
       <c r="J12" t="n">
-        <v>8556</v>
+        <v>8663</v>
       </c>
       <c r="N12" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>1835</v>
+        <v>1631</v>
       </c>
       <c r="V12" t="n">
         <v>46</v>
       </c>
       <c r="Z12" t="n">
-        <v>2117995</v>
+        <v>2182497</v>
       </c>
       <c r="AD12" t="n">
-        <v>2102987</v>
+        <v>2171473</v>
       </c>
       <c r="AH12" t="n">
-        <v>1615565</v>
+        <v>1627036</v>
       </c>
       <c r="AL12" t="n">
-        <v>74862</v>
+        <v>73898</v>
       </c>
       <c r="AP12" t="n">
-        <v>412560</v>
+        <v>470539</v>
       </c>
       <c r="AT12" t="n">
-        <v>15008</v>
+        <v>11024</v>
       </c>
       <c r="AX12" t="n">
-        <v>8277</v>
+        <v>10481</v>
       </c>
       <c r="BB12" t="n">
-        <v>8169</v>
+        <v>10381</v>
       </c>
       <c r="BF12" t="n">
-        <v>6497</v>
+        <v>7908</v>
       </c>
       <c r="BJ12" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="BN12" t="n">
-        <v>1601</v>
+        <v>2379</v>
       </c>
       <c r="BR12" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10386</v>
+        <v>9038</v>
       </c>
       <c r="F13" t="n">
-        <v>10340</v>
+        <v>8995</v>
       </c>
       <c r="J13" t="n">
-        <v>8663</v>
+        <v>7506</v>
       </c>
       <c r="N13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
-        <v>1631</v>
+        <v>1451</v>
       </c>
       <c r="V13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Z13" t="n">
-        <v>2182497</v>
+        <v>2135841</v>
       </c>
       <c r="AD13" t="n">
-        <v>2171473</v>
+        <v>2124469</v>
       </c>
       <c r="AH13" t="n">
-        <v>1627036</v>
+        <v>1464123</v>
       </c>
       <c r="AL13" t="n">
-        <v>73898</v>
+        <v>57513</v>
       </c>
       <c r="AP13" t="n">
-        <v>470539</v>
+        <v>602833</v>
       </c>
       <c r="AT13" t="n">
-        <v>11024</v>
+        <v>11372</v>
       </c>
       <c r="AX13" t="n">
-        <v>10481</v>
+        <v>8369</v>
       </c>
       <c r="BB13" t="n">
-        <v>10381</v>
+        <v>8286</v>
       </c>
       <c r="BF13" t="n">
-        <v>7908</v>
+        <v>6417</v>
       </c>
       <c r="BJ13" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="BN13" t="n">
-        <v>2379</v>
+        <v>1793</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1650,733 +1650,733 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50562</v>
+        <v>54744</v>
       </c>
       <c r="F2" t="n">
-        <v>49869</v>
+        <v>53860</v>
       </c>
       <c r="J2" t="n">
-        <v>39176</v>
+        <v>42274</v>
       </c>
       <c r="N2" t="n">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="R2" t="n">
-        <v>10344</v>
+        <v>11204</v>
       </c>
       <c r="V2" t="n">
-        <v>693</v>
+        <v>884</v>
       </c>
       <c r="Z2" t="n">
-        <v>8620259</v>
+        <v>9367997</v>
       </c>
       <c r="AD2" t="n">
-        <v>8295254</v>
+        <v>9168572</v>
       </c>
       <c r="AH2" t="n">
-        <v>6106866</v>
+        <v>6685742</v>
       </c>
       <c r="AL2" t="n">
-        <v>337654</v>
+        <v>309641</v>
       </c>
       <c r="AP2" t="n">
-        <v>1850734</v>
+        <v>2173189</v>
       </c>
       <c r="AT2" t="n">
-        <v>325005</v>
+        <v>199425</v>
       </c>
       <c r="AX2" t="n">
-        <v>55304</v>
+        <v>58125</v>
       </c>
       <c r="BB2" t="n">
-        <v>53991</v>
+        <v>56566</v>
       </c>
       <c r="BF2" t="n">
-        <v>40644</v>
+        <v>42896</v>
       </c>
       <c r="BJ2" t="n">
-        <v>697</v>
+        <v>1005</v>
       </c>
       <c r="BN2" t="n">
-        <v>12650</v>
+        <v>12665</v>
       </c>
       <c r="BR2" t="n">
-        <v>1313</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54744</v>
+        <v>53438</v>
       </c>
       <c r="F3" t="n">
-        <v>53860</v>
+        <v>52654</v>
       </c>
       <c r="J3" t="n">
-        <v>42274</v>
+        <v>41834</v>
       </c>
       <c r="N3" t="n">
-        <v>382</v>
+        <v>497</v>
       </c>
       <c r="R3" t="n">
-        <v>11204</v>
+        <v>10323</v>
       </c>
       <c r="V3" t="n">
-        <v>884</v>
+        <v>784</v>
       </c>
       <c r="Z3" t="n">
-        <v>9367997</v>
+        <v>9778252</v>
       </c>
       <c r="AD3" t="n">
-        <v>9168572</v>
+        <v>9604368</v>
       </c>
       <c r="AH3" t="n">
-        <v>6685742</v>
+        <v>7043297</v>
       </c>
       <c r="AL3" t="n">
-        <v>309641</v>
+        <v>469554</v>
       </c>
       <c r="AP3" t="n">
-        <v>2173189</v>
+        <v>2091517</v>
       </c>
       <c r="AT3" t="n">
-        <v>199425</v>
+        <v>173884</v>
       </c>
       <c r="AX3" t="n">
-        <v>58125</v>
+        <v>59150</v>
       </c>
       <c r="BB3" t="n">
-        <v>56566</v>
+        <v>57618</v>
       </c>
       <c r="BF3" t="n">
-        <v>42896</v>
+        <v>43117</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1005</v>
+        <v>687</v>
       </c>
       <c r="BN3" t="n">
-        <v>12665</v>
+        <v>13814</v>
       </c>
       <c r="BR3" t="n">
-        <v>1559</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53438</v>
+        <v>57299</v>
       </c>
       <c r="F4" t="n">
-        <v>52654</v>
+        <v>56431</v>
       </c>
       <c r="J4" t="n">
-        <v>41834</v>
+        <v>45067</v>
       </c>
       <c r="N4" t="n">
-        <v>497</v>
+        <v>419</v>
       </c>
       <c r="R4" t="n">
-        <v>10323</v>
+        <v>10945</v>
       </c>
       <c r="V4" t="n">
-        <v>784</v>
+        <v>868</v>
       </c>
       <c r="Z4" t="n">
-        <v>9778252</v>
+        <v>10385897</v>
       </c>
       <c r="AD4" t="n">
-        <v>9604368</v>
+        <v>10194623</v>
       </c>
       <c r="AH4" t="n">
-        <v>7043297</v>
+        <v>7359757</v>
       </c>
       <c r="AL4" t="n">
-        <v>469554</v>
+        <v>352831</v>
       </c>
       <c r="AP4" t="n">
-        <v>2091517</v>
+        <v>2482035</v>
       </c>
       <c r="AT4" t="n">
-        <v>173884</v>
+        <v>191274</v>
       </c>
       <c r="AX4" t="n">
-        <v>59150</v>
+        <v>58877</v>
       </c>
       <c r="BB4" t="n">
-        <v>57618</v>
+        <v>56997</v>
       </c>
       <c r="BF4" t="n">
-        <v>43117</v>
+        <v>43147</v>
       </c>
       <c r="BJ4" t="n">
-        <v>687</v>
+        <v>621</v>
       </c>
       <c r="BN4" t="n">
-        <v>13814</v>
+        <v>13229</v>
       </c>
       <c r="BR4" t="n">
-        <v>1532</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57299</v>
+        <v>43089</v>
       </c>
       <c r="F5" t="n">
-        <v>56431</v>
+        <v>42407</v>
       </c>
       <c r="J5" t="n">
-        <v>45067</v>
+        <v>33271</v>
       </c>
       <c r="N5" t="n">
-        <v>419</v>
+        <v>272</v>
       </c>
       <c r="R5" t="n">
-        <v>10945</v>
+        <v>8864</v>
       </c>
       <c r="V5" t="n">
-        <v>868</v>
+        <v>682</v>
       </c>
       <c r="Z5" t="n">
-        <v>10385897</v>
+        <v>8129264</v>
       </c>
       <c r="AD5" t="n">
-        <v>10194623</v>
+        <v>7990659</v>
       </c>
       <c r="AH5" t="n">
-        <v>7359757</v>
+        <v>5644431</v>
       </c>
       <c r="AL5" t="n">
-        <v>352831</v>
+        <v>370208</v>
       </c>
       <c r="AP5" t="n">
-        <v>2482035</v>
+        <v>1976020</v>
       </c>
       <c r="AT5" t="n">
-        <v>191274</v>
+        <v>138605</v>
       </c>
       <c r="AX5" t="n">
-        <v>58877</v>
+        <v>40817</v>
       </c>
       <c r="BB5" t="n">
-        <v>56997</v>
+        <v>39753</v>
       </c>
       <c r="BF5" t="n">
-        <v>43147</v>
+        <v>29742</v>
       </c>
       <c r="BJ5" t="n">
-        <v>621</v>
+        <v>443</v>
       </c>
       <c r="BN5" t="n">
-        <v>13229</v>
+        <v>9568</v>
       </c>
       <c r="BR5" t="n">
-        <v>1880</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43089</v>
+        <v>59261</v>
       </c>
       <c r="F6" t="n">
-        <v>42407</v>
+        <v>58227</v>
       </c>
       <c r="J6" t="n">
-        <v>33271</v>
+        <v>46120</v>
       </c>
       <c r="N6" t="n">
-        <v>272</v>
+        <v>479</v>
       </c>
       <c r="R6" t="n">
-        <v>8864</v>
+        <v>11628</v>
       </c>
       <c r="V6" t="n">
-        <v>682</v>
+        <v>1034</v>
       </c>
       <c r="Z6" t="n">
-        <v>8129264</v>
+        <v>11566816</v>
       </c>
       <c r="AD6" t="n">
-        <v>7990659</v>
+        <v>11360334</v>
       </c>
       <c r="AH6" t="n">
-        <v>5644431</v>
+        <v>7914755</v>
       </c>
       <c r="AL6" t="n">
-        <v>370208</v>
+        <v>528921</v>
       </c>
       <c r="AP6" t="n">
-        <v>1976020</v>
+        <v>2916658</v>
       </c>
       <c r="AT6" t="n">
-        <v>138605</v>
+        <v>206482</v>
       </c>
       <c r="AX6" t="n">
-        <v>40817</v>
+        <v>52829</v>
       </c>
       <c r="BB6" t="n">
-        <v>39753</v>
+        <v>51315</v>
       </c>
       <c r="BF6" t="n">
-        <v>29742</v>
+        <v>38168</v>
       </c>
       <c r="BJ6" t="n">
-        <v>443</v>
+        <v>875</v>
       </c>
       <c r="BN6" t="n">
-        <v>9568</v>
+        <v>12272</v>
       </c>
       <c r="BR6" t="n">
-        <v>1064</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59261</v>
+        <v>66960</v>
       </c>
       <c r="F7" t="n">
-        <v>58227</v>
+        <v>65863</v>
       </c>
       <c r="J7" t="n">
-        <v>46120</v>
+        <v>52198</v>
       </c>
       <c r="N7" t="n">
-        <v>479</v>
+        <v>367</v>
       </c>
       <c r="R7" t="n">
-        <v>11628</v>
+        <v>13298</v>
       </c>
       <c r="V7" t="n">
-        <v>1034</v>
+        <v>1097</v>
       </c>
       <c r="Z7" t="n">
-        <v>11566816</v>
+        <v>12252940</v>
       </c>
       <c r="AD7" t="n">
-        <v>11360334</v>
+        <v>11988179</v>
       </c>
       <c r="AH7" t="n">
-        <v>7914755</v>
+        <v>8721246</v>
       </c>
       <c r="AL7" t="n">
-        <v>528921</v>
+        <v>443243</v>
       </c>
       <c r="AP7" t="n">
-        <v>2916658</v>
+        <v>2823690</v>
       </c>
       <c r="AT7" t="n">
-        <v>206482</v>
+        <v>264761</v>
       </c>
       <c r="AX7" t="n">
-        <v>52829</v>
+        <v>67202</v>
       </c>
       <c r="BB7" t="n">
-        <v>51315</v>
+        <v>65643</v>
       </c>
       <c r="BF7" t="n">
-        <v>38168</v>
+        <v>48350</v>
       </c>
       <c r="BJ7" t="n">
-        <v>875</v>
+        <v>829</v>
       </c>
       <c r="BN7" t="n">
-        <v>12272</v>
+        <v>16464</v>
       </c>
       <c r="BR7" t="n">
-        <v>1514</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66960</v>
+        <v>55762</v>
       </c>
       <c r="F8" t="n">
-        <v>65863</v>
+        <v>54928</v>
       </c>
       <c r="J8" t="n">
-        <v>52198</v>
+        <v>43319</v>
       </c>
       <c r="N8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R8" t="n">
-        <v>13298</v>
+        <v>11241</v>
       </c>
       <c r="V8" t="n">
-        <v>1097</v>
+        <v>834</v>
       </c>
       <c r="Z8" t="n">
-        <v>12252940</v>
+        <v>10695781</v>
       </c>
       <c r="AD8" t="n">
-        <v>11988179</v>
+        <v>10510935</v>
       </c>
       <c r="AH8" t="n">
-        <v>8721246</v>
+        <v>7397618</v>
       </c>
       <c r="AL8" t="n">
-        <v>443243</v>
+        <v>265620</v>
       </c>
       <c r="AP8" t="n">
-        <v>2823690</v>
+        <v>2847697</v>
       </c>
       <c r="AT8" t="n">
-        <v>264761</v>
+        <v>184846</v>
       </c>
       <c r="AX8" t="n">
-        <v>67202</v>
+        <v>62184</v>
       </c>
       <c r="BB8" t="n">
-        <v>65643</v>
+        <v>60663</v>
       </c>
       <c r="BF8" t="n">
-        <v>48350</v>
+        <v>45493</v>
       </c>
       <c r="BJ8" t="n">
-        <v>829</v>
+        <v>1173</v>
       </c>
       <c r="BN8" t="n">
-        <v>16464</v>
+        <v>13997</v>
       </c>
       <c r="BR8" t="n">
-        <v>1559</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55762</v>
+        <v>49271</v>
       </c>
       <c r="F9" t="n">
-        <v>54928</v>
+        <v>48290</v>
       </c>
       <c r="J9" t="n">
-        <v>43319</v>
+        <v>37841</v>
       </c>
       <c r="N9" t="n">
-        <v>368</v>
+        <v>487</v>
       </c>
       <c r="R9" t="n">
-        <v>11241</v>
+        <v>9962</v>
       </c>
       <c r="V9" t="n">
-        <v>834</v>
+        <v>981</v>
       </c>
       <c r="Z9" t="n">
-        <v>10695781</v>
+        <v>9878599</v>
       </c>
       <c r="AD9" t="n">
-        <v>10510935</v>
+        <v>9608183</v>
       </c>
       <c r="AH9" t="n">
-        <v>7397618</v>
+        <v>6528887</v>
       </c>
       <c r="AL9" t="n">
-        <v>265620</v>
+        <v>545099</v>
       </c>
       <c r="AP9" t="n">
-        <v>2847697</v>
+        <v>2534197</v>
       </c>
       <c r="AT9" t="n">
-        <v>184846</v>
+        <v>270416</v>
       </c>
       <c r="AX9" t="n">
-        <v>62184</v>
+        <v>54979</v>
       </c>
       <c r="BB9" t="n">
-        <v>60663</v>
+        <v>53564</v>
       </c>
       <c r="BF9" t="n">
-        <v>45493</v>
+        <v>40101</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1173</v>
+        <v>704</v>
       </c>
       <c r="BN9" t="n">
-        <v>13997</v>
+        <v>12759</v>
       </c>
       <c r="BR9" t="n">
-        <v>1521</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49271</v>
+        <v>49384</v>
       </c>
       <c r="F10" t="n">
-        <v>48290</v>
+        <v>48585</v>
       </c>
       <c r="J10" t="n">
-        <v>37841</v>
+        <v>39330</v>
       </c>
       <c r="N10" t="n">
-        <v>487</v>
+        <v>404</v>
       </c>
       <c r="R10" t="n">
-        <v>9962</v>
+        <v>8851</v>
       </c>
       <c r="V10" t="n">
-        <v>981</v>
+        <v>799</v>
       </c>
       <c r="Z10" t="n">
-        <v>9878599</v>
+        <v>9949811</v>
       </c>
       <c r="AD10" t="n">
-        <v>9608183</v>
+        <v>9782222</v>
       </c>
       <c r="AH10" t="n">
-        <v>6528887</v>
+        <v>6665198</v>
       </c>
       <c r="AL10" t="n">
-        <v>545099</v>
+        <v>424379</v>
       </c>
       <c r="AP10" t="n">
-        <v>2534197</v>
+        <v>2692645</v>
       </c>
       <c r="AT10" t="n">
-        <v>270416</v>
+        <v>167589</v>
       </c>
       <c r="AX10" t="n">
-        <v>54979</v>
+        <v>59062</v>
       </c>
       <c r="BB10" t="n">
-        <v>53564</v>
+        <v>57801</v>
       </c>
       <c r="BF10" t="n">
-        <v>40101</v>
+        <v>42888</v>
       </c>
       <c r="BJ10" t="n">
-        <v>704</v>
+        <v>779</v>
       </c>
       <c r="BN10" t="n">
-        <v>12759</v>
+        <v>14134</v>
       </c>
       <c r="BR10" t="n">
-        <v>1415</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49384</v>
+        <v>59349</v>
       </c>
       <c r="F11" t="n">
-        <v>48585</v>
+        <v>58406</v>
       </c>
       <c r="J11" t="n">
-        <v>39330</v>
+        <v>45563</v>
       </c>
       <c r="N11" t="n">
-        <v>404</v>
+        <v>507</v>
       </c>
       <c r="R11" t="n">
-        <v>8851</v>
+        <v>12336</v>
       </c>
       <c r="V11" t="n">
-        <v>799</v>
+        <v>943</v>
       </c>
       <c r="Z11" t="n">
-        <v>9949811</v>
+        <v>11181160</v>
       </c>
       <c r="AD11" t="n">
-        <v>9782222</v>
+        <v>10983495</v>
       </c>
       <c r="AH11" t="n">
-        <v>6665198</v>
+        <v>7895166</v>
       </c>
       <c r="AL11" t="n">
-        <v>424379</v>
+        <v>477874</v>
       </c>
       <c r="AP11" t="n">
-        <v>2692645</v>
+        <v>2610455</v>
       </c>
       <c r="AT11" t="n">
-        <v>167589</v>
+        <v>197665</v>
       </c>
       <c r="AX11" t="n">
-        <v>59062</v>
+        <v>55864</v>
       </c>
       <c r="BB11" t="n">
-        <v>57801</v>
+        <v>54325</v>
       </c>
       <c r="BF11" t="n">
-        <v>42888</v>
+        <v>41522</v>
       </c>
       <c r="BJ11" t="n">
-        <v>779</v>
+        <v>602</v>
       </c>
       <c r="BN11" t="n">
-        <v>14134</v>
+        <v>12201</v>
       </c>
       <c r="BR11" t="n">
-        <v>1261</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59349</v>
+        <v>59531</v>
       </c>
       <c r="F12" t="n">
-        <v>58406</v>
+        <v>58459</v>
       </c>
       <c r="J12" t="n">
-        <v>45563</v>
+        <v>46661</v>
       </c>
       <c r="N12" t="n">
-        <v>507</v>
+        <v>458</v>
       </c>
       <c r="R12" t="n">
-        <v>12336</v>
+        <v>11340</v>
       </c>
       <c r="V12" t="n">
-        <v>943</v>
+        <v>1072</v>
       </c>
       <c r="Z12" t="n">
-        <v>11181160</v>
+        <v>11478708</v>
       </c>
       <c r="AD12" t="n">
-        <v>10983495</v>
+        <v>11150811</v>
       </c>
       <c r="AH12" t="n">
-        <v>7895166</v>
+        <v>8125195</v>
       </c>
       <c r="AL12" t="n">
-        <v>477874</v>
+        <v>408039</v>
       </c>
       <c r="AP12" t="n">
-        <v>2610455</v>
+        <v>2617577</v>
       </c>
       <c r="AT12" t="n">
-        <v>197665</v>
+        <v>327897</v>
       </c>
       <c r="AX12" t="n">
-        <v>55864</v>
+        <v>69425</v>
       </c>
       <c r="BB12" t="n">
-        <v>54325</v>
+        <v>67679</v>
       </c>
       <c r="BF12" t="n">
-        <v>41522</v>
+        <v>50582</v>
       </c>
       <c r="BJ12" t="n">
-        <v>602</v>
+        <v>762</v>
       </c>
       <c r="BN12" t="n">
-        <v>12201</v>
+        <v>16335</v>
       </c>
       <c r="BR12" t="n">
-        <v>1539</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59531</v>
+        <v>51136</v>
       </c>
       <c r="F13" t="n">
-        <v>58459</v>
+        <v>50280</v>
       </c>
       <c r="J13" t="n">
-        <v>46661</v>
+        <v>40010</v>
       </c>
       <c r="N13" t="n">
-        <v>458</v>
+        <v>317</v>
       </c>
       <c r="R13" t="n">
-        <v>11340</v>
+        <v>9953</v>
       </c>
       <c r="V13" t="n">
-        <v>1072</v>
+        <v>856</v>
       </c>
       <c r="Z13" t="n">
-        <v>11478708</v>
+        <v>10512598</v>
       </c>
       <c r="AD13" t="n">
-        <v>11150811</v>
+        <v>10325574</v>
       </c>
       <c r="AH13" t="n">
-        <v>8125195</v>
+        <v>6934991</v>
       </c>
       <c r="AL13" t="n">
-        <v>408039</v>
+        <v>467731</v>
       </c>
       <c r="AP13" t="n">
-        <v>2617577</v>
+        <v>2922852</v>
       </c>
       <c r="AT13" t="n">
-        <v>327897</v>
+        <v>187024</v>
       </c>
       <c r="AX13" t="n">
-        <v>69425</v>
+        <v>56554</v>
       </c>
       <c r="BB13" t="n">
-        <v>67679</v>
+        <v>55114</v>
       </c>
       <c r="BF13" t="n">
-        <v>50582</v>
+        <v>42064</v>
       </c>
       <c r="BJ13" t="n">
-        <v>762</v>
+        <v>610</v>
       </c>
       <c r="BN13" t="n">
-        <v>16335</v>
+        <v>12440</v>
       </c>
       <c r="BR13" t="n">
-        <v>1746</v>
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
